--- a/masuratori.xlsx
+++ b/masuratori.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="16">
   <si>
     <t xml:space="preserve">f</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t xml:space="preserve">white noise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mas 4</t>
   </si>
 </sst>
 </file>
@@ -266,7 +269,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="11.23046875" defaultRowHeight="14.35" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -646,6 +649,215 @@
     <row r="25" customFormat="false" ht="14.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="J27" s="0" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>94.4</v>
+      </c>
+      <c r="F28" s="0" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="H28" s="0" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="I28" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>94.6</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <v>91.1</v>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <v>94.1</v>
+      </c>
+      <c r="H29" s="0" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>92.2</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>96.4</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>97.9</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="H30" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="I30" s="0" t="n">
+        <v>94.9</v>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>89.8</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>96.6</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="H31" s="0" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="I31" s="0" t="n">
+        <v>95.4</v>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>91.5</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>91.4</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="H32" s="0" t="n">
+        <v>99</v>
+      </c>
+      <c r="I32" s="0" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>90.1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>94</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>96.4</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>92.4</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>96.4</v>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>88.3</v>
       </c>
     </row>
   </sheetData>
